--- a/analysis/data/raw_data/data_measurements_01.xlsx
+++ b/analysis/data/raw_data/data_measurements_01.xlsx
@@ -3522,10 +3522,10 @@
         <v>43.2</v>
       </c>
       <c r="P22" t="n">
-        <v>21095.97696</v>
+        <v>13625.1549866667</v>
       </c>
       <c r="Q22" t="n">
-        <v>21.09597696</v>
+        <v>13.6251549866667</v>
       </c>
     </row>
     <row r="23">
@@ -3573,10 +3573,10 @@
         <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>261.666666666667</v>
+        <v>54.4266666666667</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.261666666666667</v>
+        <v>0.0544266666666667</v>
       </c>
     </row>
     <row r="24">
@@ -5540,10 +5540,10 @@
         <v>26.4</v>
       </c>
       <c r="P62" t="n">
-        <v>4814.59968</v>
+        <v>3098.13333333333</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.81459968</v>
+        <v>3.09813333333333</v>
       </c>
     </row>
     <row r="63">
@@ -5591,10 +5591,10 @@
         <v>28.4</v>
       </c>
       <c r="P63" t="n">
-        <v>5993.81621333333</v>
+        <v>5867.19466666666</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.99381621333333</v>
+        <v>5.86719466666666</v>
       </c>
     </row>
     <row r="64">
@@ -6142,10 +6142,10 @@
         <v>25.2</v>
       </c>
       <c r="P74" t="n">
-        <v>4187.45376</v>
+        <v>3689.99402666667</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.18745376</v>
+        <v>3.68999402666667</v>
       </c>
     </row>
     <row r="75">
@@ -6193,10 +6193,10 @@
         <v>22</v>
       </c>
       <c r="P75" t="n">
-        <v>2786.22666666667</v>
+        <v>1268.02410666667</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.78622666666667</v>
+        <v>1.26802410666667</v>
       </c>
     </row>
     <row r="76">
@@ -6446,10 +6446,10 @@
         <v>38.4</v>
       </c>
       <c r="P80" t="n">
-        <v>14816.37888</v>
+        <v>16203.60576</v>
       </c>
       <c r="Q80" t="n">
-        <v>14.81637888</v>
+        <v>16.20360576</v>
       </c>
     </row>
     <row r="81">
@@ -6495,10 +6495,10 @@
         <v>32.4</v>
       </c>
       <c r="P81" t="n">
-        <v>8899.86528</v>
+        <v>9064.66922666667</v>
       </c>
       <c r="Q81" t="n">
-        <v>8.89986528</v>
+        <v>9.06466922666666</v>
       </c>
     </row>
     <row r="82">
@@ -6544,10 +6544,10 @@
         <v>34</v>
       </c>
       <c r="P82" t="n">
-        <v>10284.5466666667</v>
+        <v>9378.13333333333</v>
       </c>
       <c r="Q82" t="n">
-        <v>10.2845466666667</v>
+        <v>9.37813333333333</v>
       </c>
     </row>
     <row r="83">
@@ -6885,10 +6885,10 @@
         <v>25.2</v>
       </c>
       <c r="P89" t="n">
-        <v>4187.45376</v>
+        <v>4486.33152</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.18745376</v>
+        <v>4.48633152</v>
       </c>
     </row>
     <row r="90">
@@ -6934,10 +6934,10 @@
         <v>25.6</v>
       </c>
       <c r="P90" t="n">
-        <v>4390.03818666667</v>
+        <v>4595.75424</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.39003818666667</v>
+        <v>4.59575424</v>
       </c>
     </row>
     <row r="91">
@@ -7052,7 +7052,7 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F93" t="s">
         <v>141</v>
@@ -7081,10 +7081,10 @@
         <v>28.8</v>
       </c>
       <c r="P93" t="n">
-        <v>6250.65984</v>
+        <v>5471.136</v>
       </c>
       <c r="Q93" t="n">
-        <v>6.25065984</v>
+        <v>5.471136</v>
       </c>
     </row>
     <row r="94">
@@ -7179,10 +7179,10 @@
         <v>28</v>
       </c>
       <c r="P95" t="n">
-        <v>5744.10666666667</v>
+        <v>5007.38730666667</v>
       </c>
       <c r="Q95" t="n">
-        <v>5.74410666666667</v>
+        <v>5.00738730666667</v>
       </c>
     </row>
     <row r="96">
@@ -7326,10 +7326,10 @@
         <v>13.2</v>
       </c>
       <c r="P98" t="n">
-        <v>601.82496</v>
+        <v>519.984</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.60182496</v>
+        <v>0.519984</v>
       </c>
     </row>
     <row r="99">
@@ -7473,10 +7473,10 @@
         <v>23.2</v>
       </c>
       <c r="P101" t="n">
-        <v>3267.47562666667</v>
+        <v>1497.55392</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.26747562666667</v>
+        <v>1.49755392</v>
       </c>
     </row>
     <row r="102">
@@ -7493,7 +7493,7 @@
         <v>2</v>
       </c>
       <c r="E102" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F102" t="s">
         <v>20</v>
@@ -7522,10 +7522,10 @@
         <v>17.2</v>
       </c>
       <c r="P102" t="n">
-        <v>1331.47722666667</v>
+        <v>919.559466666666</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.33147722666667</v>
+        <v>0.919559466666666</v>
       </c>
     </row>
     <row r="103">
@@ -7669,10 +7669,10 @@
         <v>17.2</v>
       </c>
       <c r="P105" t="n">
-        <v>1331.47722666667</v>
+        <v>1377.91573333333</v>
       </c>
       <c r="Q105" t="n">
-        <v>1.33147722666667</v>
+        <v>1.37791573333333</v>
       </c>
     </row>
     <row r="106">
@@ -7816,10 +7816,10 @@
         <v>26</v>
       </c>
       <c r="P108" t="n">
-        <v>4599.05333333333</v>
+        <v>5755.36042666667</v>
       </c>
       <c r="Q108" t="n">
-        <v>4.59905333333333</v>
+        <v>5.75536042666667</v>
       </c>
     </row>
     <row r="109">
@@ -7836,7 +7836,7 @@
         <v>2</v>
       </c>
       <c r="E109" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F109" t="s">
         <v>52</v>
@@ -7865,10 +7865,10 @@
         <v>32.8</v>
       </c>
       <c r="P109" t="n">
-        <v>9233.57610666667</v>
+        <v>5295.56394666667</v>
       </c>
       <c r="Q109" t="n">
-        <v>9.23357610666667</v>
+        <v>5.29556394666667</v>
       </c>
     </row>
     <row r="110">
@@ -7967,10 +7967,10 @@
         <v>24.8</v>
       </c>
       <c r="P111" t="n">
-        <v>3991.19957333333</v>
+        <v>2662.31808</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.99119957333333</v>
+        <v>2.66231808</v>
       </c>
     </row>
     <row r="112">
@@ -8069,10 +8069,10 @@
         <v>22.8</v>
       </c>
       <c r="P113" t="n">
-        <v>3101.36544</v>
+        <v>2214.74666666667</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.10136544</v>
+        <v>2.21474666666667</v>
       </c>
     </row>
     <row r="114">
@@ -8120,10 +8120,10 @@
         <v>26</v>
       </c>
       <c r="P114" t="n">
-        <v>4599.05333333333</v>
+        <v>1558.41130666667</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.59905333333333</v>
+        <v>1.55841130666667</v>
       </c>
     </row>
     <row r="115">
@@ -8171,10 +8171,10 @@
         <v>26.8</v>
       </c>
       <c r="P115" t="n">
-        <v>5036.77770666667</v>
+        <v>1616.48874666667</v>
       </c>
       <c r="Q115" t="n">
-        <v>5.03677770666667</v>
+        <v>1.61648874666667</v>
       </c>
     </row>
     <row r="116">
@@ -8477,10 +8477,10 @@
         <v>34.4</v>
       </c>
       <c r="P121" t="n">
-        <v>10651.8178133333</v>
+        <v>7356.47573333333</v>
       </c>
       <c r="Q121" t="n">
-        <v>10.6518178133333</v>
+        <v>7.35647573333333</v>
       </c>
     </row>
     <row r="122">
@@ -8497,7 +8497,7 @@
         <v>1</v>
       </c>
       <c r="E122" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F122" t="s">
         <v>91</v>
@@ -8528,10 +8528,10 @@
         <v>32.4</v>
       </c>
       <c r="P122" t="n">
-        <v>8899.86528</v>
+        <v>2478.67413333333</v>
       </c>
       <c r="Q122" t="n">
-        <v>8.89986528</v>
+        <v>2.47867413333333</v>
       </c>
     </row>
     <row r="123">
@@ -8548,10 +8548,10 @@
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F123" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G123" t="s">
         <v>92</v>
@@ -8579,10 +8579,10 @@
         <v>41.2</v>
       </c>
       <c r="P123" t="n">
-        <v>18299.5348266667</v>
+        <v>2962.55232</v>
       </c>
       <c r="Q123" t="n">
-        <v>18.2995348266667</v>
+        <v>2.96255232</v>
       </c>
     </row>
     <row r="124">
@@ -9140,10 +9140,10 @@
         <v>24.4</v>
       </c>
       <c r="P134" t="n">
-        <v>3801.17514666667</v>
+        <v>1153.008</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.80117514666667</v>
+        <v>1.153008</v>
       </c>
     </row>
     <row r="135">
@@ -9344,10 +9344,10 @@
         <v>17.2</v>
       </c>
       <c r="P138" t="n">
-        <v>1331.47722666667</v>
+        <v>1192.36266666667</v>
       </c>
       <c r="Q138" t="n">
-        <v>1.33147722666667</v>
+        <v>1.19236266666667</v>
       </c>
     </row>
     <row r="139">
@@ -9415,7 +9415,7 @@
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F140" t="s">
         <v>91</v>
@@ -9446,10 +9446,10 @@
         <v>33.6</v>
       </c>
       <c r="P140" t="n">
-        <v>9925.81632</v>
+        <v>2587.49397333333</v>
       </c>
       <c r="Q140" t="n">
-        <v>9.92581632</v>
+        <v>2.58749397333333</v>
       </c>
     </row>
     <row r="141">
@@ -9466,10 +9466,10 @@
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F141" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G141" t="s">
         <v>92</v>
@@ -9497,10 +9497,10 @@
         <v>33.6</v>
       </c>
       <c r="P141" t="n">
-        <v>9925.81632</v>
+        <v>2840.23466666667</v>
       </c>
       <c r="Q141" t="n">
-        <v>9.92581632</v>
+        <v>2.84023466666667</v>
       </c>
     </row>
     <row r="142">
@@ -10007,10 +10007,10 @@
         <v>25.6</v>
       </c>
       <c r="P151" t="n">
-        <v>4390.03818666667</v>
+        <v>2972.53333333333</v>
       </c>
       <c r="Q151" t="n">
-        <v>4.39003818666667</v>
+        <v>2.97253333333333</v>
       </c>
     </row>
     <row r="152">
@@ -10060,10 +10060,10 @@
         <v>34</v>
       </c>
       <c r="P152" t="n">
-        <v>10284.5466666667</v>
+        <v>6212.10901333333</v>
       </c>
       <c r="Q152" t="n">
-        <v>10.2845466666667</v>
+        <v>6.21210901333333</v>
       </c>
     </row>
     <row r="153">
@@ -10239,10 +10239,10 @@
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F156" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G156" t="s">
         <v>92</v>
@@ -10270,10 +10270,10 @@
         <v>30.4</v>
       </c>
       <c r="P156" t="n">
-        <v>7351.38474666667</v>
+        <v>3984.90282666667</v>
       </c>
       <c r="Q156" t="n">
-        <v>7.35138474666667</v>
+        <v>3.98490282666667</v>
       </c>
     </row>
     <row r="157">
@@ -10674,10 +10674,10 @@
         <v>23.2</v>
       </c>
       <c r="P164" t="n">
-        <v>3267.47562666667</v>
+        <v>4104.13909333333</v>
       </c>
       <c r="Q164" t="n">
-        <v>3.26747562666667</v>
+        <v>4.10413909333333</v>
       </c>
     </row>
     <row r="165">
@@ -10949,10 +10949,10 @@
         <v>1</v>
       </c>
       <c r="E170" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F170" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="G170" t="s">
         <v>92</v>
@@ -10980,10 +10980,10 @@
         <v>48</v>
       </c>
       <c r="P170" t="n">
-        <v>28938.24</v>
+        <v>5122.60437333333</v>
       </c>
       <c r="Q170" t="n">
-        <v>28.93824</v>
+        <v>5.12260437333333</v>
       </c>
     </row>
     <row r="171">
@@ -11494,10 +11494,10 @@
         <v>10</v>
       </c>
       <c r="P180" t="n">
-        <v>261.666666666667</v>
+        <v>447.370453333333</v>
       </c>
       <c r="Q180" t="n">
-        <v>0.261666666666667</v>
+        <v>0.447370453333333</v>
       </c>
     </row>
     <row r="181">
@@ -11698,10 +11698,10 @@
         <v>19.2</v>
       </c>
       <c r="P184" t="n">
-        <v>1852.04736</v>
+        <v>2310.77205333333</v>
       </c>
       <c r="Q184" t="n">
-        <v>1.85204736</v>
+        <v>2.31077205333333</v>
       </c>
     </row>
     <row r="185">
@@ -11749,10 +11749,10 @@
         <v>30.4</v>
       </c>
       <c r="P185" t="n">
-        <v>7351.38474666667</v>
+        <v>7931.22133333333</v>
       </c>
       <c r="Q185" t="n">
-        <v>7.35138474666667</v>
+        <v>7.93122133333333</v>
       </c>
     </row>
     <row r="186">
@@ -11902,10 +11902,10 @@
         <v>31.2</v>
       </c>
       <c r="P188" t="n">
-        <v>7947.16416</v>
+        <v>10063.8088533333</v>
       </c>
       <c r="Q188" t="n">
-        <v>7.94716416</v>
+        <v>10.0638088533333</v>
       </c>
     </row>
     <row r="189">
@@ -15502,10 +15502,10 @@
         <v>22.8</v>
       </c>
       <c r="P260" t="n">
-        <v>3101.36544</v>
+        <v>1905.40224</v>
       </c>
       <c r="Q260" t="n">
-        <v>3.10136544</v>
+        <v>1.90540224</v>
       </c>
     </row>
     <row r="261">
@@ -15551,10 +15551,10 @@
         <v>24</v>
       </c>
       <c r="P261" t="n">
-        <v>3617.28</v>
+        <v>2546.56512</v>
       </c>
       <c r="Q261" t="n">
-        <v>3.61728</v>
+        <v>2.54656512</v>
       </c>
     </row>
     <row r="262">
@@ -15649,10 +15649,10 @@
         <v>18</v>
       </c>
       <c r="P263" t="n">
-        <v>1526.04</v>
+        <v>1172.83605333333</v>
       </c>
       <c r="Q263" t="n">
-        <v>1.52604</v>
+        <v>1.17283605333333</v>
       </c>
     </row>
     <row r="264">
@@ -15698,10 +15698,10 @@
         <v>26</v>
       </c>
       <c r="P264" t="n">
-        <v>4599.05333333333</v>
+        <v>2447.82677333333</v>
       </c>
       <c r="Q264" t="n">
-        <v>4.59905333333333</v>
+        <v>2.44782677333333</v>
       </c>
     </row>
     <row r="265">
@@ -15747,10 +15747,10 @@
         <v>25.6</v>
       </c>
       <c r="P265" t="n">
-        <v>4390.03818666667</v>
+        <v>3571.19317333333</v>
       </c>
       <c r="Q265" t="n">
-        <v>4.39003818666667</v>
+        <v>3.57119317333333</v>
       </c>
     </row>
     <row r="266">
@@ -15796,10 +15796,10 @@
         <v>34.8</v>
       </c>
       <c r="P266" t="n">
-        <v>11027.73024</v>
+        <v>6756.54314666667</v>
       </c>
       <c r="Q266" t="n">
-        <v>11.02773024</v>
+        <v>6.75654314666667</v>
       </c>
     </row>
     <row r="267">
@@ -15845,10 +15845,10 @@
         <v>20</v>
       </c>
       <c r="P267" t="n">
-        <v>2093.33333333333</v>
+        <v>1473.70666666667</v>
       </c>
       <c r="Q267" t="n">
-        <v>2.09333333333333</v>
+        <v>1.47370666666667</v>
       </c>
     </row>
     <row r="268">
@@ -15894,10 +15894,10 @@
         <v>25.2</v>
       </c>
       <c r="P268" t="n">
-        <v>4187.45376</v>
+        <v>2909.73333333333</v>
       </c>
       <c r="Q268" t="n">
-        <v>4.18745376</v>
+        <v>2.90973333333333</v>
       </c>
     </row>
     <row r="269">
@@ -15914,7 +15914,7 @@
         <v>2</v>
       </c>
       <c r="E269" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F269" t="s">
         <v>20</v>
@@ -15943,10 +15943,10 @@
         <v>30</v>
       </c>
       <c r="P269" t="n">
-        <v>7065</v>
+        <v>4973.76</v>
       </c>
       <c r="Q269" t="n">
-        <v>7.065</v>
+        <v>4.97376</v>
       </c>
     </row>
     <row r="270">
@@ -16747,7 +16747,7 @@
         <v>1</v>
       </c>
       <c r="E286" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F286" t="s">
         <v>235</v>
@@ -16776,10 +16776,10 @@
         <v>31.6</v>
       </c>
       <c r="P286" t="n">
-        <v>8256.75978666667</v>
+        <v>2181.21984</v>
       </c>
       <c r="Q286" t="n">
-        <v>8.25675978666667</v>
+        <v>2.18121984</v>
       </c>
     </row>
     <row r="287">
@@ -16796,7 +16796,7 @@
         <v>1</v>
       </c>
       <c r="E287" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F287" t="s">
         <v>20</v>
@@ -16825,10 +16825,10 @@
         <v>23.2</v>
       </c>
       <c r="P287" t="n">
-        <v>3267.47562666667</v>
+        <v>958.445226666666</v>
       </c>
       <c r="Q287" t="n">
-        <v>3.26747562666667</v>
+        <v>0.958445226666666</v>
       </c>
     </row>
     <row r="288">
@@ -16874,10 +16874,10 @@
         <v>24</v>
       </c>
       <c r="P288" t="n">
-        <v>3617.28</v>
+        <v>1268.99541333333</v>
       </c>
       <c r="Q288" t="n">
-        <v>3.61728</v>
+        <v>1.26899541333333</v>
       </c>
     </row>
     <row r="289">
@@ -16894,7 +16894,7 @@
         <v>1</v>
       </c>
       <c r="E289" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F289" t="s">
         <v>20</v>
@@ -16923,10 +16923,10 @@
         <v>36.8</v>
       </c>
       <c r="P289" t="n">
-        <v>13040.4283733333</v>
+        <v>4398.61248</v>
       </c>
       <c r="Q289" t="n">
-        <v>13.0404283733333</v>
+        <v>4.39861248</v>
       </c>
     </row>
     <row r="290">
@@ -16943,7 +16943,7 @@
         <v>1</v>
       </c>
       <c r="E290" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F290" t="s">
         <v>20</v>
@@ -16972,10 +16972,10 @@
         <v>20.4</v>
       </c>
       <c r="P290" t="n">
-        <v>2221.46208</v>
+        <v>926.928</v>
       </c>
       <c r="Q290" t="n">
-        <v>2.22146208</v>
+        <v>0.926928</v>
       </c>
     </row>
     <row r="291">
@@ -17021,10 +17021,10 @@
         <v>14</v>
       </c>
       <c r="P291" t="n">
-        <v>718.013333333333</v>
+        <v>336.373546666667</v>
       </c>
       <c r="Q291" t="n">
-        <v>0.718013333333333</v>
+        <v>0.336373546666667</v>
       </c>
     </row>
     <row r="292">
@@ -17041,7 +17041,7 @@
         <v>1</v>
       </c>
       <c r="E292" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F292" t="s">
         <v>20</v>
@@ -17070,10 +17070,10 @@
         <v>18</v>
       </c>
       <c r="P292" t="n">
-        <v>1526.04</v>
+        <v>702.422186666666</v>
       </c>
       <c r="Q292" t="n">
-        <v>1.52604</v>
+        <v>0.702422186666666</v>
       </c>
     </row>
     <row r="293">
@@ -17119,10 +17119,10 @@
         <v>24.8</v>
       </c>
       <c r="P293" t="n">
-        <v>3991.19957333333</v>
+        <v>1789.48181333333</v>
       </c>
       <c r="Q293" t="n">
-        <v>3.99119957333333</v>
+        <v>1.78948181333333</v>
       </c>
     </row>
     <row r="294">
@@ -17139,7 +17139,7 @@
         <v>1</v>
       </c>
       <c r="E294" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F294" t="s">
         <v>136</v>
@@ -17168,10 +17168,10 @@
         <v>18</v>
       </c>
       <c r="P294" t="n">
-        <v>1526.04</v>
+        <v>616.980693333333</v>
       </c>
       <c r="Q294" t="n">
-        <v>1.52604</v>
+        <v>0.616980693333333</v>
       </c>
     </row>
     <row r="295">
@@ -17188,7 +17188,7 @@
         <v>1</v>
       </c>
       <c r="E295" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F295" t="s">
         <v>20</v>
@@ -17217,10 +17217,10 @@
         <v>34</v>
       </c>
       <c r="P295" t="n">
-        <v>10284.5466666667</v>
+        <v>1114.12224</v>
       </c>
       <c r="Q295" t="n">
-        <v>10.2845466666667</v>
+        <v>1.11412224</v>
       </c>
     </row>
     <row r="296">
@@ -17237,7 +17237,7 @@
         <v>1</v>
       </c>
       <c r="E296" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F296" t="s">
         <v>20</v>
@@ -17266,10 +17266,10 @@
         <v>20.8</v>
       </c>
       <c r="P296" t="n">
-        <v>2354.71530666667</v>
+        <v>636.64128</v>
       </c>
       <c r="Q296" t="n">
-        <v>2.35471530666667</v>
+        <v>0.63664128</v>
       </c>
     </row>
     <row r="297">
@@ -17286,7 +17286,7 @@
         <v>1</v>
       </c>
       <c r="E297" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F297" t="s">
         <v>20</v>
@@ -17315,10 +17315,10 @@
         <v>38</v>
       </c>
       <c r="P297" t="n">
-        <v>14358.1733333333</v>
+        <v>4572.24192</v>
       </c>
       <c r="Q297" t="n">
-        <v>14.3581733333333</v>
+        <v>4.57224192</v>
       </c>
     </row>
     <row r="298">
@@ -17335,7 +17335,7 @@
         <v>1</v>
       </c>
       <c r="E298" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F298" t="s">
         <v>117</v>
@@ -17364,10 +17364,10 @@
         <v>45.6</v>
       </c>
       <c r="P298" t="n">
-        <v>24810.92352</v>
+        <v>5244.52010666667</v>
       </c>
       <c r="Q298" t="n">
-        <v>24.81092352</v>
+        <v>5.24452010666667</v>
       </c>
     </row>
     <row r="299">
@@ -17384,7 +17384,7 @@
         <v>1</v>
       </c>
       <c r="E299" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F299" t="s">
         <v>117</v>
@@ -17413,10 +17413,10 @@
         <v>32</v>
       </c>
       <c r="P299" t="n">
-        <v>8574.29333333333</v>
+        <v>3177.31157333333</v>
       </c>
       <c r="Q299" t="n">
-        <v>8.57429333333333</v>
+        <v>3.17731157333333</v>
       </c>
     </row>
     <row r="300">
@@ -17433,7 +17433,7 @@
         <v>1</v>
       </c>
       <c r="E300" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F300" t="s">
         <v>136</v>
@@ -17462,10 +17462,10 @@
         <v>20.8</v>
       </c>
       <c r="P300" t="n">
-        <v>2354.71530666667</v>
+        <v>840.280746666667</v>
       </c>
       <c r="Q300" t="n">
-        <v>2.35471530666667</v>
+        <v>0.840280746666667</v>
       </c>
     </row>
     <row r="301">
@@ -17482,7 +17482,7 @@
         <v>1</v>
       </c>
       <c r="E301" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F301" t="s">
         <v>20</v>
@@ -17511,10 +17511,10 @@
         <v>30</v>
       </c>
       <c r="P301" t="n">
-        <v>7065</v>
+        <v>2261.03445333333</v>
       </c>
       <c r="Q301" t="n">
-        <v>7.065</v>
+        <v>2.26103445333333</v>
       </c>
     </row>
     <row r="302">
@@ -17531,7 +17531,7 @@
         <v>1</v>
       </c>
       <c r="E302" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F302" t="s">
         <v>20</v>
@@ -17560,10 +17560,10 @@
         <v>29.6</v>
       </c>
       <c r="P302" t="n">
-        <v>6786.15125333333</v>
+        <v>1819.75978666667</v>
       </c>
       <c r="Q302" t="n">
-        <v>6.78615125333333</v>
+        <v>1.81975978666667</v>
       </c>
     </row>
     <row r="303">
@@ -17580,7 +17580,7 @@
         <v>1</v>
       </c>
       <c r="E303" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="F303" t="s">
         <v>20</v>
@@ -17609,10 +17609,10 @@
         <v>22</v>
       </c>
       <c r="P303" t="n">
-        <v>2786.22666666667</v>
+        <v>786.791893333333</v>
       </c>
       <c r="Q303" t="n">
-        <v>2.78622666666667</v>
+        <v>0.786791893333333</v>
       </c>
     </row>
     <row r="304">
@@ -17658,10 +17658,10 @@
         <v>24.8</v>
       </c>
       <c r="P304" t="n">
-        <v>3991.19957333333</v>
+        <v>1175.616</v>
       </c>
       <c r="Q304" t="n">
-        <v>3.99119957333333</v>
+        <v>1.175616</v>
       </c>
     </row>
     <row r="305">
@@ -17707,10 +17707,10 @@
         <v>12</v>
       </c>
       <c r="P305" t="n">
-        <v>452.16</v>
+        <v>362.263893333333</v>
       </c>
       <c r="Q305" t="n">
-        <v>0.45216</v>
+        <v>0.362263893333333</v>
       </c>
     </row>
     <row r="306">
@@ -17756,10 +17756,10 @@
         <v>14</v>
       </c>
       <c r="P306" t="n">
-        <v>718.013333333333</v>
+        <v>390.66624</v>
       </c>
       <c r="Q306" t="n">
-        <v>0.718013333333333</v>
+        <v>0.39066624</v>
       </c>
     </row>
     <row r="307">
@@ -18884,7 +18884,7 @@
         <v>1</v>
       </c>
       <c r="E329" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F329" t="s">
         <v>20</v>
@@ -18915,10 +18915,10 @@
         <v>39.6</v>
       </c>
       <c r="P329" t="n">
-        <v>16249.27392</v>
+        <v>4803.74784</v>
       </c>
       <c r="Q329" t="n">
-        <v>16.24927392</v>
+        <v>4.80374784</v>
       </c>
     </row>
     <row r="330">
@@ -18935,7 +18935,7 @@
         <v>1</v>
       </c>
       <c r="E330" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F330" t="s">
         <v>20</v>
@@ -18966,10 +18966,10 @@
         <v>33.2</v>
       </c>
       <c r="P330" t="n">
-        <v>9575.52629333334</v>
+        <v>4761.2448</v>
       </c>
       <c r="Q330" t="n">
-        <v>9.57552629333334</v>
+        <v>4.7612448</v>
       </c>
     </row>
     <row r="331">
@@ -19017,10 +19017,10 @@
         <v>36</v>
       </c>
       <c r="P331" t="n">
-        <v>12208.32</v>
+        <v>10584.8311466667</v>
       </c>
       <c r="Q331" t="n">
-        <v>12.20832</v>
+        <v>10.5848311466667</v>
       </c>
     </row>
     <row r="332">
@@ -20449,10 +20449,10 @@
         <v>14</v>
       </c>
       <c r="P359" t="n">
-        <v>718.013333333333</v>
+        <v>336.373546666667</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.718013333333333</v>
+        <v>0.336373546666667</v>
       </c>
     </row>
     <row r="360">
@@ -21489,7 +21489,7 @@
         <v>2</v>
       </c>
       <c r="E380" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F380" t="s">
         <v>91</v>
@@ -21520,10 +21520,10 @@
         <v>14.4</v>
       </c>
       <c r="P380" t="n">
-        <v>781.33248</v>
+        <v>1214.13333333333</v>
       </c>
       <c r="Q380" t="n">
-        <v>0.78133248</v>
+        <v>1.21413333333333</v>
       </c>
     </row>
     <row r="381">
@@ -21571,10 +21571,10 @@
         <v>20.4</v>
       </c>
       <c r="P381" t="n">
-        <v>2221.46208</v>
+        <v>2417.24736</v>
       </c>
       <c r="Q381" t="n">
-        <v>2.22146208</v>
+        <v>2.41724736</v>
       </c>
     </row>
     <row r="382">
@@ -22187,7 +22187,7 @@
         <v>1</v>
       </c>
       <c r="E394" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="F394" t="s">
         <v>20</v>
@@ -22218,10 +22218,10 @@
         <v>62.4</v>
       </c>
       <c r="P394" t="n">
-        <v>63577.31328</v>
+        <v>9418.86122666667</v>
       </c>
       <c r="Q394" t="n">
-        <v>63.57731328</v>
+        <v>9.41886122666667</v>
       </c>
     </row>
     <row r="395">
@@ -22667,10 +22667,10 @@
         <v>32.4</v>
       </c>
       <c r="P403" t="n">
-        <v>8899.86528</v>
+        <v>6455.94048</v>
       </c>
       <c r="Q403" t="n">
-        <v>8.89986528</v>
+        <v>6.45594048</v>
       </c>
     </row>
     <row r="404">
@@ -27737,7 +27737,7 @@
         <v>2</v>
       </c>
       <c r="E510" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F510" t="s">
         <v>91</v>
@@ -27768,10 +27768,10 @@
         <v>14</v>
       </c>
       <c r="P510" t="n">
-        <v>718.013333333333</v>
+        <v>1245.24864</v>
       </c>
       <c r="Q510" t="n">
-        <v>0.718013333333333</v>
+        <v>1.24524864</v>
       </c>
     </row>
     <row r="511">
@@ -30410,10 +30410,10 @@
         <v>18.4</v>
       </c>
       <c r="P562" t="n">
-        <v>1630.05354666667</v>
+        <v>2626.14528</v>
       </c>
       <c r="Q562" t="n">
-        <v>1.63005354666667</v>
+        <v>2.62614528</v>
       </c>
     </row>
     <row r="563">
@@ -30653,10 +30653,10 @@
         <v>9.6</v>
       </c>
       <c r="P567" t="n">
-        <v>231.50592</v>
+        <v>367.823786666667</v>
       </c>
       <c r="Q567" t="n">
-        <v>0.23150592</v>
+        <v>0.367823786666667</v>
       </c>
     </row>
     <row r="568">
@@ -32091,7 +32091,7 @@
         <v>2</v>
       </c>
       <c r="E604" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F604" t="s">
         <v>136</v>
@@ -32120,10 +32120,10 @@
         <v>30.4</v>
       </c>
       <c r="P604" t="n">
-        <v>7351.38474666667</v>
+        <v>5343.05749333333</v>
       </c>
       <c r="Q604" t="n">
-        <v>7.35138474666667</v>
+        <v>5.34305749333333</v>
       </c>
     </row>
     <row r="605">
@@ -32169,10 +32169,10 @@
         <v>49.6</v>
       </c>
       <c r="P605" t="n">
-        <v>31929.5965866667</v>
+        <v>21298.54464</v>
       </c>
       <c r="Q605" t="n">
-        <v>31.9295965866667</v>
+        <v>21.29854464</v>
       </c>
     </row>
     <row r="606">
@@ -32218,10 +32218,10 @@
         <v>48.8</v>
       </c>
       <c r="P606" t="n">
-        <v>30409.4011733333</v>
+        <v>20835.5328</v>
       </c>
       <c r="Q606" t="n">
-        <v>30.4094011733333</v>
+        <v>20.8355328</v>
       </c>
     </row>
     <row r="607">

--- a/analysis/data/raw_data/data_measurements_01.xlsx
+++ b/analysis/data/raw_data/data_measurements_01.xlsx
@@ -260,6 +260,9 @@
     <t xml:space="preserve">V36</t>
   </si>
   <si>
+    <t xml:space="preserve">d</t>
+  </si>
+  <si>
     <t xml:space="preserve">V37</t>
   </si>
   <si>
@@ -288,9 +291,6 @@
   </si>
   <si>
     <t xml:space="preserve">V45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d</t>
   </si>
   <si>
     <t xml:space="preserve">V46</t>
@@ -3108,7 +3108,7 @@
         <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -3959,7 +3959,7 @@
         <v>46</v>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G25" t="s">
         <v>61</v>
@@ -4644,7 +4644,7 @@
         <v>6</v>
       </c>
       <c r="G37" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s">
         <v>38</v>
@@ -4687,7 +4687,7 @@
         <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
         <v>57</v>
@@ -4744,7 +4744,7 @@
         <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D39" t="s">
         <v>57</v>
@@ -4801,7 +4801,7 @@
         <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
         <v>57</v>
@@ -4858,7 +4858,7 @@
         <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D41" t="s">
         <v>57</v>
@@ -4915,7 +4915,7 @@
         <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D42" t="s">
         <v>57</v>
@@ -4970,7 +4970,7 @@
         <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
         <v>57</v>
@@ -5025,7 +5025,7 @@
         <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
         <v>57</v>
@@ -5082,7 +5082,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D45" t="s">
         <v>57</v>
@@ -5097,10 +5097,10 @@
         <v>29</v>
       </c>
       <c r="H45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J45" t="s">
         <v>36</v>
@@ -5139,7 +5139,7 @@
         <v>43</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>57</v>
@@ -5151,7 +5151,7 @@
         <v>5</v>
       </c>
       <c r="G46" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s">
         <v>38</v>
@@ -5538,7 +5538,7 @@
         <v>3</v>
       </c>
       <c r="G53" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s">
         <v>103</v>
@@ -5595,7 +5595,7 @@
         <v>5</v>
       </c>
       <c r="G54" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s">
         <v>71</v>
@@ -6391,7 +6391,7 @@
         <v>10</v>
       </c>
       <c r="G68" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s">
         <v>71</v>
@@ -6560,13 +6560,13 @@
         <v>10</v>
       </c>
       <c r="G71" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s">
         <v>71</v>
       </c>
       <c r="I71" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J71"/>
       <c r="K71"/>
@@ -7668,13 +7668,13 @@
         <v>5</v>
       </c>
       <c r="G91" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s">
         <v>153</v>
       </c>
       <c r="I91" t="s">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="J91"/>
       <c r="K91"/>
@@ -9283,7 +9283,7 @@
         <v>6</v>
       </c>
       <c r="G120" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H120" t="s">
         <v>54</v>
@@ -9457,10 +9457,10 @@
         <v>23</v>
       </c>
       <c r="H123" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="I123" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J123" t="s">
         <v>136</v>
@@ -10483,10 +10483,10 @@
         <v>23</v>
       </c>
       <c r="H141" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="I141" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J141" t="s">
         <v>36</v>
@@ -11346,10 +11346,10 @@
         <v>23</v>
       </c>
       <c r="H156" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="I156" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J156" t="s">
         <v>36</v>
@@ -11972,7 +11972,7 @@
         <v>71</v>
       </c>
       <c r="I167" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J167" t="s">
         <v>136</v>
@@ -12140,10 +12140,10 @@
         <v>23</v>
       </c>
       <c r="H170" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="I170" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J170" t="s">
         <v>136</v>
@@ -12194,7 +12194,7 @@
         <v>9</v>
       </c>
       <c r="G171" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H171" t="s">
         <v>103</v>
@@ -12308,7 +12308,7 @@
         <v>5</v>
       </c>
       <c r="G173" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H173" t="s">
         <v>24</v>
@@ -14199,7 +14199,7 @@
         <v>290</v>
       </c>
       <c r="I206" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="J206" t="s">
         <v>36</v>
@@ -14256,7 +14256,7 @@
         <v>290</v>
       </c>
       <c r="I207" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="J207" t="s">
         <v>36</v>
@@ -14313,7 +14313,7 @@
         <v>290</v>
       </c>
       <c r="I208" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="J208" t="s">
         <v>36</v>
@@ -14421,13 +14421,13 @@
         <v>5</v>
       </c>
       <c r="G210" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H210" t="s">
         <v>290</v>
       </c>
       <c r="I210" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="J210" t="s">
         <v>36</v>
@@ -14535,7 +14535,7 @@
         <v>9</v>
       </c>
       <c r="G212" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H212" t="s">
         <v>256</v>
@@ -15108,10 +15108,10 @@
         <v>29</v>
       </c>
       <c r="H222" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I222" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J222" t="s">
         <v>36</v>
@@ -15881,7 +15881,7 @@
         <v>5</v>
       </c>
       <c r="G236" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H236" t="s">
         <v>63</v>
@@ -15936,7 +15936,7 @@
         <v>5</v>
       </c>
       <c r="G237" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H237" t="s">
         <v>24</v>
@@ -15991,7 +15991,7 @@
         <v>5</v>
       </c>
       <c r="G238" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H238" t="s">
         <v>153</v>
@@ -16101,7 +16101,7 @@
         <v>5</v>
       </c>
       <c r="G240" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H240" t="s">
         <v>24</v>
@@ -16156,7 +16156,7 @@
         <v>5</v>
       </c>
       <c r="G241" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H241" t="s">
         <v>24</v>
@@ -16211,7 +16211,7 @@
         <v>5</v>
       </c>
       <c r="G242" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H242" t="s">
         <v>153</v>
@@ -16266,7 +16266,7 @@
         <v>5</v>
       </c>
       <c r="G243" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H243" t="s">
         <v>24</v>
@@ -16651,7 +16651,7 @@
         <v>5</v>
       </c>
       <c r="G250" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H250" t="s">
         <v>258</v>
@@ -16706,7 +16706,7 @@
         <v>5</v>
       </c>
       <c r="G251" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H251" t="s">
         <v>24</v>
@@ -16926,7 +16926,7 @@
         <v>5</v>
       </c>
       <c r="G255" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H255" t="s">
         <v>24</v>
@@ -16981,7 +16981,7 @@
         <v>5</v>
       </c>
       <c r="G256" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H256" t="s">
         <v>24</v>
@@ -17036,7 +17036,7 @@
         <v>5</v>
       </c>
       <c r="G257" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H257" t="s">
         <v>63</v>
@@ -17091,7 +17091,7 @@
         <v>5</v>
       </c>
       <c r="G258" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H258" t="s">
         <v>24</v>
@@ -17146,7 +17146,7 @@
         <v>5</v>
       </c>
       <c r="G259" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H259" t="s">
         <v>153</v>
@@ -19893,7 +19893,7 @@
         <v>46</v>
       </c>
       <c r="F309" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G309" t="s">
         <v>75</v>
@@ -19925,10 +19925,10 @@
         <v>66</v>
       </c>
       <c r="R309" t="n">
-        <v>160486.656</v>
+        <v>150456.24</v>
       </c>
       <c r="S309" t="n">
-        <v>160.486656</v>
+        <v>150.45624</v>
       </c>
     </row>
     <row r="310">
@@ -19948,7 +19948,7 @@
         <v>46</v>
       </c>
       <c r="F310" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G310" t="s">
         <v>29</v>
@@ -19980,10 +19980,10 @@
         <v>29.2</v>
       </c>
       <c r="R310" t="n">
-        <v>13386.448</v>
+        <v>13029.4760533333</v>
       </c>
       <c r="S310" t="n">
-        <v>13.386448</v>
+        <v>13.0294760533333</v>
       </c>
     </row>
     <row r="311">
@@ -22062,7 +22062,7 @@
         <v>71</v>
       </c>
       <c r="I347" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J347" t="s">
         <v>36</v>
@@ -22575,7 +22575,7 @@
         <v>464</v>
       </c>
       <c r="I356" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J356" t="s">
         <v>36</v>
@@ -22629,10 +22629,10 @@
         <v>23</v>
       </c>
       <c r="H357" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I357" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J357" t="s">
         <v>36</v>
@@ -22917,7 +22917,7 @@
         <v>464</v>
       </c>
       <c r="I362" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J362" t="s">
         <v>36</v>
@@ -22974,7 +22974,7 @@
         <v>464</v>
       </c>
       <c r="I363" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J363" t="s">
         <v>36</v>
@@ -23031,7 +23031,7 @@
         <v>464</v>
       </c>
       <c r="I364" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J364" t="s">
         <v>36</v>
@@ -23259,7 +23259,7 @@
         <v>290</v>
       </c>
       <c r="I368" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="J368" t="s">
         <v>36</v>
@@ -23316,7 +23316,7 @@
         <v>464</v>
       </c>
       <c r="I369" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J369" t="s">
         <v>36</v>
@@ -23601,7 +23601,7 @@
         <v>290</v>
       </c>
       <c r="I374" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="J374" t="s">
         <v>36</v>
@@ -24664,7 +24664,7 @@
         <v>3</v>
       </c>
       <c r="G393" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H393" t="s">
         <v>38</v>
@@ -25173,7 +25173,7 @@
         <v>290</v>
       </c>
       <c r="I402" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="J402"/>
       <c r="K402"/>
@@ -25393,7 +25393,7 @@
         <v>4</v>
       </c>
       <c r="G406" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H406" t="s">
         <v>34</v>
@@ -25450,7 +25450,7 @@
         <v>4</v>
       </c>
       <c r="G407" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H407" t="s">
         <v>34</v>
@@ -25511,7 +25511,7 @@
         <v>71</v>
       </c>
       <c r="I408" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J408" t="s">
         <v>136</v>
@@ -25629,7 +25629,7 @@
         <v>71</v>
       </c>
       <c r="I410" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J410"/>
       <c r="K410" t="s">
@@ -25846,16 +25846,16 @@
         <v>46</v>
       </c>
       <c r="F414" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G414" t="s">
         <v>29</v>
       </c>
       <c r="H414" t="s">
-        <v>24</v>
+        <v>242</v>
       </c>
       <c r="I414" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="J414"/>
       <c r="K414" t="s">
@@ -25880,10 +25880,10 @@
         <v>30.8</v>
       </c>
       <c r="R414" t="n">
-        <v>15290.8119466667</v>
+        <v>7645.40597333333</v>
       </c>
       <c r="S414" t="n">
-        <v>15.2908119466667</v>
+        <v>7.64540597333333</v>
       </c>
     </row>
     <row r="415">
@@ -25903,16 +25903,16 @@
         <v>46</v>
       </c>
       <c r="F415" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G415" t="s">
         <v>29</v>
       </c>
       <c r="H415" t="s">
-        <v>24</v>
+        <v>242</v>
       </c>
       <c r="I415" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="J415"/>
       <c r="K415" t="s">
@@ -25960,16 +25960,16 @@
         <v>46</v>
       </c>
       <c r="F416" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G416" t="s">
         <v>23</v>
       </c>
       <c r="H416" t="s">
-        <v>24</v>
+        <v>242</v>
       </c>
       <c r="I416" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="J416" t="s">
         <v>36</v>
@@ -25996,10 +25996,10 @@
         <v>19.2</v>
       </c>
       <c r="R416" t="n">
-        <v>3704.09472</v>
+        <v>1852.04736</v>
       </c>
       <c r="S416" t="n">
-        <v>3.70409472</v>
+        <v>1.85204736</v>
       </c>
     </row>
     <row r="417">
@@ -30574,7 +30574,7 @@
         <v>71</v>
       </c>
       <c r="I503" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J503"/>
       <c r="K503"/>
@@ -33014,10 +33014,10 @@
         <v>29</v>
       </c>
       <c r="H546" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I546" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J546"/>
       <c r="K546"/>
@@ -33636,7 +33636,7 @@
         <v>71</v>
       </c>
       <c r="I557" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="J557" t="s">
         <v>136</v>
@@ -35012,10 +35012,10 @@
       </c>
       <c r="G584"/>
       <c r="H584" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I584" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J584"/>
       <c r="K584"/>
@@ -35062,7 +35062,7 @@
         <v>71</v>
       </c>
       <c r="I585" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="J585"/>
       <c r="K585"/>
@@ -35192,7 +35192,7 @@
         <v>22</v>
       </c>
       <c r="F588" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G588"/>
       <c r="H588"/>
@@ -36158,7 +36158,7 @@
         <v>5</v>
       </c>
       <c r="G609" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H609" t="s">
         <v>38</v>
@@ -36323,7 +36323,7 @@
         <v>4</v>
       </c>
       <c r="G612" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H612" t="s">
         <v>153</v>

--- a/analysis/data/raw_data/data_measurements_01.xlsx
+++ b/analysis/data/raw_data/data_measurements_01.xlsx
@@ -14190,7 +14190,7 @@
         <v>46</v>
       </c>
       <c r="F206" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G206" t="s">
         <v>29</v>
@@ -14418,7 +14418,7 @@
         <v>46</v>
       </c>
       <c r="F210" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G210" t="s">
         <v>82</v>

--- a/analysis/data/raw_data/data_measurements_01.xlsx
+++ b/analysis/data/raw_data/data_measurements_01.xlsx
@@ -14190,7 +14190,7 @@
         <v>46</v>
       </c>
       <c r="F206" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G206" t="s">
         <v>29</v>
@@ -14418,7 +14418,7 @@
         <v>46</v>
       </c>
       <c r="F210" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G210" t="s">
         <v>82</v>

--- a/analysis/data/raw_data/data_measurements_01.xlsx
+++ b/analysis/data/raw_data/data_measurements_01.xlsx
@@ -5374,7 +5374,7 @@
         <v>46</v>
       </c>
       <c r="F50" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G50"/>
       <c r="H50" t="s">
@@ -7227,7 +7227,7 @@
         <v>46</v>
       </c>
       <c r="F83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G83"/>
       <c r="H83" t="s">
@@ -20174,7 +20174,7 @@
         <v>46</v>
       </c>
       <c r="F314" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G314"/>
       <c r="H314" t="s">
@@ -27326,7 +27326,7 @@
         <v>46</v>
       </c>
       <c r="F440" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G440"/>
       <c r="H440" t="s">
@@ -27377,7 +27377,7 @@
         <v>46</v>
       </c>
       <c r="F441" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G441"/>
       <c r="H441" t="s">
@@ -27428,7 +27428,7 @@
         <v>46</v>
       </c>
       <c r="F442" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G442"/>
       <c r="H442" t="s">
@@ -27479,7 +27479,7 @@
         <v>46</v>
       </c>
       <c r="F443" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G443"/>
       <c r="H443" t="s">
@@ -27530,7 +27530,7 @@
         <v>46</v>
       </c>
       <c r="F444" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G444"/>
       <c r="H444" t="s">
@@ -27581,7 +27581,7 @@
         <v>46</v>
       </c>
       <c r="F445" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G445"/>
       <c r="H445" t="s">
@@ -27632,7 +27632,7 @@
         <v>46</v>
       </c>
       <c r="F446" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G446"/>
       <c r="H446" t="s">
@@ -27683,7 +27683,7 @@
         <v>46</v>
       </c>
       <c r="F447" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G447"/>
       <c r="H447" t="s">
@@ -27734,7 +27734,7 @@
         <v>46</v>
       </c>
       <c r="F448" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G448"/>
       <c r="H448" t="s">
@@ -27785,7 +27785,7 @@
         <v>46</v>
       </c>
       <c r="F449" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G449"/>
       <c r="H449" t="s">
@@ -27836,7 +27836,7 @@
         <v>46</v>
       </c>
       <c r="F450" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G450"/>
       <c r="H450" t="s">
@@ -27887,7 +27887,7 @@
         <v>46</v>
       </c>
       <c r="F451" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G451"/>
       <c r="H451" t="s">
@@ -27936,7 +27936,7 @@
         <v>46</v>
       </c>
       <c r="F452" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G452"/>
       <c r="H452" t="s">
@@ -27985,7 +27985,7 @@
         <v>46</v>
       </c>
       <c r="F453" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G453"/>
       <c r="H453" t="s">
@@ -28034,7 +28034,7 @@
         <v>46</v>
       </c>
       <c r="F454" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G454"/>
       <c r="H454" t="s">
@@ -28083,7 +28083,7 @@
         <v>46</v>
       </c>
       <c r="F455" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G455"/>
       <c r="H455" t="s">
@@ -28132,7 +28132,7 @@
         <v>46</v>
       </c>
       <c r="F456" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G456"/>
       <c r="H456" t="s">
@@ -28181,7 +28181,7 @@
         <v>46</v>
       </c>
       <c r="F457" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G457"/>
       <c r="H457" t="s">
@@ -28230,7 +28230,7 @@
         <v>46</v>
       </c>
       <c r="F458" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G458"/>
       <c r="H458" t="s">
@@ -28279,7 +28279,7 @@
         <v>46</v>
       </c>
       <c r="F459" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G459"/>
       <c r="H459" t="s">
@@ -28328,7 +28328,7 @@
         <v>46</v>
       </c>
       <c r="F460" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G460"/>
       <c r="H460" t="s">
@@ -28377,7 +28377,7 @@
         <v>46</v>
       </c>
       <c r="F461" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G461"/>
       <c r="H461" t="s">
@@ -28426,7 +28426,7 @@
         <v>46</v>
       </c>
       <c r="F462" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G462"/>
       <c r="H462" t="s">
@@ -28475,7 +28475,7 @@
         <v>46</v>
       </c>
       <c r="F463" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G463"/>
       <c r="H463" t="s">
@@ -28524,7 +28524,7 @@
         <v>46</v>
       </c>
       <c r="F464" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G464"/>
       <c r="H464" t="s">
@@ -28573,7 +28573,7 @@
         <v>46</v>
       </c>
       <c r="F465" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G465"/>
       <c r="H465" t="s">
@@ -28622,7 +28622,7 @@
         <v>46</v>
       </c>
       <c r="F466" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G466"/>
       <c r="H466" t="s">
@@ -28671,7 +28671,7 @@
         <v>46</v>
       </c>
       <c r="F467" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G467"/>
       <c r="H467" t="s">
@@ -28720,7 +28720,7 @@
         <v>46</v>
       </c>
       <c r="F468" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G468"/>
       <c r="H468" t="s">
@@ -28769,7 +28769,7 @@
         <v>46</v>
       </c>
       <c r="F469" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G469"/>
       <c r="H469" t="s">
@@ -28820,7 +28820,7 @@
         <v>46</v>
       </c>
       <c r="F470" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G470"/>
       <c r="H470" t="s">
@@ -29148,7 +29148,7 @@
         <v>46</v>
       </c>
       <c r="F476" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G476"/>
       <c r="H476" t="s">
@@ -29201,7 +29201,7 @@
         <v>46</v>
       </c>
       <c r="F477" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G477"/>
       <c r="H477" t="s">
@@ -29254,7 +29254,7 @@
         <v>46</v>
       </c>
       <c r="F478" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G478"/>
       <c r="H478" t="s">
@@ -29702,7 +29702,7 @@
         <v>46</v>
       </c>
       <c r="F486" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G486"/>
       <c r="H486" t="s">
@@ -29753,7 +29753,7 @@
         <v>46</v>
       </c>
       <c r="F487" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G487"/>
       <c r="H487" t="s">
@@ -29804,7 +29804,7 @@
         <v>46</v>
       </c>
       <c r="F488" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G488"/>
       <c r="H488" t="s">
@@ -29857,7 +29857,7 @@
         <v>46</v>
       </c>
       <c r="F489" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G489"/>
       <c r="H489" t="s">
@@ -29906,7 +29906,7 @@
         <v>46</v>
       </c>
       <c r="F490" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G490"/>
       <c r="H490" t="s">
@@ -29957,7 +29957,7 @@
         <v>46</v>
       </c>
       <c r="F491" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G491"/>
       <c r="H491" t="s">
@@ -30008,7 +30008,7 @@
         <v>46</v>
       </c>
       <c r="F492" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G492"/>
       <c r="H492" t="s">
@@ -30059,7 +30059,7 @@
         <v>46</v>
       </c>
       <c r="F493" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G493"/>
       <c r="H493" t="s">
@@ -30110,7 +30110,7 @@
         <v>46</v>
       </c>
       <c r="F494" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G494"/>
       <c r="H494" t="s">
@@ -30161,7 +30161,7 @@
         <v>46</v>
       </c>
       <c r="F495" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G495"/>
       <c r="H495" t="s">
@@ -30212,7 +30212,7 @@
         <v>46</v>
       </c>
       <c r="F496" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G496"/>
       <c r="H496" t="s">
@@ -30263,7 +30263,7 @@
         <v>46</v>
       </c>
       <c r="F497" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G497"/>
       <c r="H497" t="s">
@@ -30314,7 +30314,7 @@
         <v>46</v>
       </c>
       <c r="F498" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G498"/>
       <c r="H498" t="s">
@@ -30365,7 +30365,7 @@
         <v>46</v>
       </c>
       <c r="F499" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G499"/>
       <c r="H499" t="s">
@@ -30416,7 +30416,7 @@
         <v>46</v>
       </c>
       <c r="F500" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G500"/>
       <c r="H500" t="s">
@@ -30465,7 +30465,7 @@
         <v>46</v>
       </c>
       <c r="F501" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G501"/>
       <c r="H501" t="s">
@@ -30516,7 +30516,7 @@
         <v>46</v>
       </c>
       <c r="F502" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G502"/>
       <c r="H502" t="s">
@@ -33973,7 +33973,7 @@
         <v>46</v>
       </c>
       <c r="F563" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G563"/>
       <c r="H563" t="s">
@@ -34138,7 +34138,7 @@
         <v>46</v>
       </c>
       <c r="F566" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G566"/>
       <c r="H566" t="s">
